--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
@@ -442,7 +442,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -622,6 +622,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -631,7 +634,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -810,6 +813,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="59">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="60">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -853,7 +859,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1033,6 +1039,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1042,7 +1051,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1222,6 +1231,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>2263014.35528298</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2307327.5016448041</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1264,7 +1276,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1444,6 +1456,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1453,7 +1468,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1633,6 +1648,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>913646.19172686804</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>957959.33808869217</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1654,11 +1672,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99720192"/>
-        <c:axId val="103724160"/>
+        <c:axId val="479046272"/>
+        <c:axId val="494485888"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99720192"/>
+        <c:axId val="479046272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1701,14 +1719,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="103724160"/>
+        <c:crossAx val="494485888"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="103724160"/>
+        <c:axId val="494485888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1759,7 +1777,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99720192"/>
+        <c:crossAx val="479046272"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1920,7 +1938,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2100,6 +2118,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>-72114.733350567156</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-120278.52715325328</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2114,8 +2135,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="401867904"/>
-        <c:axId val="399842304"/>
+        <c:axId val="620743296"/>
+        <c:axId val="620741376"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2140,7 +2161,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2320,6 +2341,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>46171</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>46203</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2329,7 +2353,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="60"/>
+                <c:ptCount val="61"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2509,6 +2533,9 @@
                 </c:pt>
                 <c:pt idx="59">
                   <c:v>1.2450000047683716</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1.2760000228881836</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2525,11 +2552,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="399531392"/>
-        <c:axId val="399840384"/>
+        <c:axId val="619971712"/>
+        <c:axId val="619973632"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="399531392"/>
+        <c:axId val="619971712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2572,14 +2599,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399840384"/>
+        <c:crossAx val="619973632"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="399840384"/>
+        <c:axId val="619973632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2630,12 +2657,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="399531392"/>
+        <c:crossAx val="619971712"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="399842304"/>
+        <c:axId val="620741376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2672,12 +2699,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401867904"/>
+        <c:crossAx val="620743296"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="401867904"/>
+        <c:axId val="620743296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2686,7 +2713,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="399842304"/>
+        <c:crossAx val="620741376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3095,7 +3122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG62"/>
+  <dimension ref="A1:AG63"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5899,6 +5926,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="63" spans="1:13" ht="12.75">
+      <c r="A63" s="11">
+        <v>46203</v>
+      </c>
+      <c r="B63" s="12">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="C63" s="12">
+        <v>41.799999239999998</v>
+      </c>
+      <c r="D63" s="13">
+        <v>26.574869220600849</v>
+      </c>
+      <c r="E63" s="13">
+        <v>-120278.52715325328</v>
+      </c>
+      <c r="F63" s="14">
+        <v>-94262.166924579549</v>
+      </c>
+      <c r="G63" s="14">
+        <v>1335193.3317966722</v>
+      </c>
+      <c r="H63" s="14">
+        <v>1703706.7219327039</v>
+      </c>
+      <c r="I63" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J63" s="14">
+        <v>2307327.5016448041</v>
+      </c>
+      <c r="K63" s="14">
+        <v>957959.33808869217</v>
+      </c>
+      <c r="L63" s="13">
+        <v>603620.77971210016</v>
+      </c>
+      <c r="M63" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
@@ -442,7 +442,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -625,6 +625,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -634,7 +637,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -816,6 +819,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="60">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="61">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -859,7 +865,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1042,6 +1048,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1051,7 +1060,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1234,6 +1243,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>2307327.5016448041</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2081679.7890976393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1276,7 +1288,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1459,6 +1471,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1468,7 +1483,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1651,6 +1666,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>957959.33808869217</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>732311.62554152729</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1672,11 +1690,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="479046272"/>
-        <c:axId val="494485888"/>
+        <c:axId val="521881088"/>
+        <c:axId val="541883008"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="479046272"/>
+        <c:axId val="521881088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1719,14 +1737,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="494485888"/>
+        <c:crossAx val="541883008"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="494485888"/>
+        <c:axId val="541883008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1777,7 +1795,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="479046272"/>
+        <c:crossAx val="521881088"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1938,7 +1956,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2121,6 +2139,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>-120278.52715325328</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-70500.180121343234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2135,8 +2156,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="620743296"/>
-        <c:axId val="620741376"/>
+        <c:axId val="678416768"/>
+        <c:axId val="676457088"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2161,7 +2182,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2344,6 +2365,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>46203</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>46234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2353,7 +2377,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="61"/>
+                <c:ptCount val="62"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2536,6 +2560,9 @@
                 </c:pt>
                 <c:pt idx="60">
                   <c:v>1.2760000228881836</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1.1069999933242798</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2552,11 +2579,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="619971712"/>
-        <c:axId val="619973632"/>
+        <c:axId val="572603392"/>
+        <c:axId val="676455168"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="619971712"/>
+        <c:axId val="572603392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2599,14 +2626,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="619973632"/>
+        <c:crossAx val="676455168"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="619973632"/>
+        <c:axId val="676455168"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2657,12 +2684,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="619971712"/>
+        <c:crossAx val="572603392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="620741376"/>
+        <c:axId val="676457088"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2699,12 +2726,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620743296"/>
+        <c:crossAx val="678416768"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="620743296"/>
+        <c:axId val="678416768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2713,7 +2740,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="620741376"/>
+        <c:crossAx val="676457088"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3122,7 +3149,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG63"/>
+  <dimension ref="A1:AG64"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -5967,6 +5994,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:13" ht="12.75">
+      <c r="A64" s="11">
+        <v>46234</v>
+      </c>
+      <c r="B64" s="12">
+        <v>1.1069999933242798</v>
+      </c>
+      <c r="C64" s="12">
+        <v>35.700000760000002</v>
+      </c>
+      <c r="D64" s="13">
+        <v>26.77592732691858</v>
+      </c>
+      <c r="E64" s="13">
+        <v>-70500.180121343234</v>
+      </c>
+      <c r="F64" s="14">
+        <v>-63685.799951663794</v>
+      </c>
+      <c r="G64" s="14">
+        <v>1271507.5318450085</v>
+      </c>
+      <c r="H64" s="14">
+        <v>1407558.8292641959</v>
+      </c>
+      <c r="I64" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J64" s="14">
+        <v>2081679.7890976393</v>
+      </c>
+      <c r="K64" s="14">
+        <v>732311.62554152729</v>
+      </c>
+      <c r="L64" s="13">
+        <v>674120.9598334434</v>
+      </c>
+      <c r="M64" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">

--- a/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
+++ b/lai/valuationquan/szseinnovation100ETF/szseinnovation100ETFmodel2(SAR).xlsx
@@ -442,7 +442,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -628,6 +628,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -637,7 +640,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -822,6 +825,9 @@
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
                 <c:pt idx="61">
+                  <c:v>1349368.163556112</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>1349368.163556112</c:v>
                 </c:pt>
               </c:numCache>
@@ -865,7 +871,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1051,6 +1057,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1060,7 +1069,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1246,6 +1255,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>2081679.7890976393</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2090580.3030172242</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1288,7 +1300,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -1474,6 +1486,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1483,7 +1498,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1669,6 +1684,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>732311.62554152729</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>741212.13946111221</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1690,11 +1708,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="521881088"/>
-        <c:axId val="541883008"/>
+        <c:axId val="395067776"/>
+        <c:axId val="413639424"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="521881088"/>
+        <c:axId val="395067776"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1737,14 +1755,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="541883008"/>
+        <c:crossAx val="413639424"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="541883008"/>
+        <c:axId val="413639424"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1795,7 +1813,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="521881088"/>
+        <c:crossAx val="395067776"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1956,7 +1974,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!买卖</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -2142,6 +2160,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>-70500.180121343234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-69892.34544564558</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2156,8 +2177,8 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="678416768"/>
-        <c:axId val="676457088"/>
+        <c:axId val="489279872"/>
+        <c:axId val="485509376"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -2182,7 +2203,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>44377</c:v>
                 </c:pt>
@@ -2368,6 +2389,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>46234</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>46265</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2377,7 +2401,7 @@
               <c:f>'model2(1)&amp;SAR_manual_oper'!指数</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="62"/>
+                <c:ptCount val="63"/>
                 <c:pt idx="0">
                   <c:v>1.0309999999999999</c:v>
                 </c:pt>
@@ -2563,6 +2587,9 @@
                 </c:pt>
                 <c:pt idx="61">
                   <c:v>1.1069999933242798</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1.1139999628067017</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2579,11 +2606,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="572603392"/>
-        <c:axId val="676455168"/>
+        <c:axId val="429222912"/>
+        <c:axId val="485507840"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="572603392"/>
+        <c:axId val="429222912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2626,14 +2653,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="676455168"/>
+        <c:crossAx val="485507840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="676455168"/>
+        <c:axId val="485507840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2684,12 +2711,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="572603392"/>
+        <c:crossAx val="429222912"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="676457088"/>
+        <c:axId val="485509376"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2726,12 +2753,12 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="678416768"/>
+        <c:crossAx val="489279872"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="678416768"/>
+        <c:axId val="489279872"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2740,7 +2767,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="676457088"/>
+        <c:crossAx val="485509376"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3149,7 +3176,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AG64"/>
+  <dimension ref="A1:AG65"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="10" customWidth="1"/>
@@ -6035,6 +6062,47 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:13" ht="12.75">
+      <c r="A65" s="11">
+        <v>46265</v>
+      </c>
+      <c r="B65" s="12">
+        <v>1.1139999628067017</v>
+      </c>
+      <c r="C65" s="12">
+        <v>35.77999878</v>
+      </c>
+      <c r="D65" s="13">
+        <v>26.932866445108154</v>
+      </c>
+      <c r="E65" s="13">
+        <v>-69892.34544564558</v>
+      </c>
+      <c r="F65" s="14">
+        <v>-62739.989029760065</v>
+      </c>
+      <c r="G65" s="14">
+        <v>1208767.5428152485</v>
+      </c>
+      <c r="H65" s="14">
+        <v>1346566.997738135</v>
+      </c>
+      <c r="I65" s="14">
+        <v>1349368.163556112</v>
+      </c>
+      <c r="J65" s="14">
+        <v>2090580.3030172242</v>
+      </c>
+      <c r="K65" s="14">
+        <v>741212.13946111221</v>
+      </c>
+      <c r="L65" s="13">
+        <v>744013.30527908902</v>
+      </c>
+      <c r="M65" s="8">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="H2">
